--- a/Template.xlsx
+++ b/Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34b6dee9d188c71f/CV/Github/Scheduler/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34b6dee9d188c71f/Projects/Github/Scheduler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{822E7D6E-81BD-46DF-83BA-C33D2D78659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53F45C95-24ED-4B97-ADFE-9CF278CF5EF2}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{822E7D6E-81BD-46DF-83BA-C33D2D78659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12FF4563-DC28-45D5-8DCA-9F114D025C97}"/>
   <bookViews>
-    <workbookView xWindow="4710" yWindow="2160" windowWidth="21600" windowHeight="17235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4995" yWindow="3000" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="New20256APP(final)" sheetId="3" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="67">
   <si>
     <t>Day</t>
   </si>
@@ -211,6 +211,42 @@
   <si>
     <t>Complete schedule blue days, black nights</t>
   </si>
+  <si>
+    <t>britt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David </t>
+  </si>
+  <si>
+    <t>david</t>
+  </si>
+  <si>
+    <t>josh</t>
+  </si>
+  <si>
+    <t>liz</t>
+  </si>
+  <si>
+    <t>Josh</t>
+  </si>
+  <si>
+    <t>megan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">britt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">david </t>
+  </si>
+  <si>
+    <t xml:space="preserve">josh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Britt </t>
+  </si>
+  <si>
+    <t>ashley</t>
+  </si>
 </sst>
 </file>
 
@@ -275,19 +311,22 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,8 +381,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2CEEF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED973"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6425B"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADADAD"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -491,11 +572,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
@@ -563,13 +655,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -940,40 +1070,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9E3936-17BB-4D73-87AF-4DD3E416CF32}">
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="20"/>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="30"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="44"/>
       <c r="I1" s="21"/>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="30"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44"/>
       <c r="Q1" s="21"/>
-      <c r="R1" s="28" t="s">
+      <c r="R1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="31"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="45"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
@@ -1047,368 +1177,407 @@
       <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>11</v>
+      <c r="B3" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>56</v>
       </c>
       <c r="I3" s="22">
         <v>1</v>
       </c>
-      <c r="J3" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" s="25" t="s">
-        <v>13</v>
-      </c>
+      <c r="J3" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="28"/>
+      <c r="M3" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" s="28"/>
+      <c r="P3" s="27"/>
       <c r="Q3" s="22">
         <v>1</v>
       </c>
-      <c r="R3" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="S3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="U3" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="V3" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="W3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="X3" s="25" t="s">
-        <v>15</v>
+      <c r="R3" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="T3" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="V3" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="W3" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="X3" s="32" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="22">
         <v>2</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>10</v>
+      <c r="B4" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>61</v>
       </c>
       <c r="I4" s="22">
         <v>2</v>
       </c>
-      <c r="J4" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="25" t="s">
-        <v>12</v>
+      <c r="J4" s="27"/>
+      <c r="K4" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="28"/>
+      <c r="M4" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="Q4" s="22">
         <v>2</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="S4" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="T4" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="X4" s="25" t="s">
-        <v>14</v>
+      <c r="R4" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="T4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="U4" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="W4" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="X4" s="33" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
         <v>3</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>11</v>
+      <c r="B5" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>60</v>
       </c>
       <c r="I5" s="22">
         <v>3</v>
       </c>
-      <c r="J5" s="25" t="s">
-        <v>12</v>
-      </c>
+      <c r="J5" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="27"/>
       <c r="Q5" s="22">
         <v>3</v>
       </c>
-      <c r="R5" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="V5" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
+      <c r="R5" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="S5" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="T5" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="U5" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="V5" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X5" s="34" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <v>4</v>
       </c>
-      <c r="B6" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>10</v>
+      <c r="B6" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>13</v>
       </c>
       <c r="I6" s="22">
         <v>4</v>
       </c>
-      <c r="K6" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="P6" s="25" t="s">
-        <v>12</v>
+      <c r="J6" s="27"/>
+      <c r="K6" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="P6" s="32" t="s">
+        <v>60</v>
       </c>
       <c r="Q6" s="22">
         <v>4</v>
       </c>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="T6" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="U6" s="25"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="X6" s="25" t="s">
-        <v>15</v>
+      <c r="R6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="S6" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="T6" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="U6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="V6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="W6" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="X6" s="31" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
         <v>5</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="25" t="s">
+      <c r="B7" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="31" t="s">
         <v>11</v>
       </c>
       <c r="I7" s="22">
         <v>5</v>
       </c>
-      <c r="J7" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>13</v>
-      </c>
+      <c r="J7" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="28"/>
+      <c r="M7" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="O7" s="28"/>
+      <c r="P7" s="27"/>
       <c r="Q7" s="22">
         <v>5</v>
       </c>
-      <c r="R7" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="T7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="U7" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="V7" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="X7" s="25" t="s">
-        <v>14</v>
+      <c r="R7" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="T7" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="U7" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="V7" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="W7" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="X7" s="33" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <v>6</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>10</v>
+      <c r="B8" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>61</v>
       </c>
       <c r="I8" s="22">
         <v>6</v>
       </c>
-      <c r="J8" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="N8" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="O8" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="P8" s="25" t="s">
-        <v>12</v>
+      <c r="J8" s="27"/>
+      <c r="K8" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="28"/>
+      <c r="M8" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="Q8" s="22">
         <v>6</v>
       </c>
-      <c r="R8" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T8" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="U8" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="V8" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="W8" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="X8" s="25" t="s">
+      <c r="R8" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="T8" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="U8" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="V8" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X8" s="34" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1416,388 +1585,615 @@
       <c r="A9" s="22">
         <v>7</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="25" t="s">
+      <c r="B9" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="38" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="22">
         <v>7</v>
       </c>
-      <c r="J9" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>13</v>
-      </c>
+      <c r="J9" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="O9" s="28"/>
+      <c r="P9" s="27"/>
       <c r="Q9" s="22">
         <v>7</v>
       </c>
-      <c r="R9" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="S9" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="T9" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="U9" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="V9" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W9" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="X9" s="25" t="s">
-        <v>14</v>
+      <c r="R9" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="S9" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="T9" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="U9" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="V9" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="W9" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="X9" s="33" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <v>8</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>10</v>
+      <c r="B10" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>58</v>
       </c>
       <c r="I10" s="22">
         <v>8</v>
       </c>
-      <c r="O10" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="P10" s="25" t="s">
-        <v>12</v>
+      <c r="J10" s="27"/>
+      <c r="K10" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="Q10" s="22">
         <v>8</v>
       </c>
-      <c r="R10" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="S10" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T10" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="U10" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="V10" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="W10" s="25"/>
-      <c r="X10" s="25"/>
+      <c r="R10" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="S10" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="T10" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="U10" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="V10" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="W10" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="X10" s="37" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
         <v>9</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="25" t="s">
+      <c r="B11" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="31" t="s">
         <v>11</v>
       </c>
       <c r="I11" s="22">
         <v>9</v>
       </c>
-      <c r="J11" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N11" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="O11" s="26" t="s">
-        <v>13</v>
-      </c>
+      <c r="J11" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="27"/>
       <c r="Q11" s="22">
         <v>9</v>
       </c>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T11" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="U11" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="V11" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="W11" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="X11" s="25" t="s">
-        <v>15</v>
+      <c r="R11" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="S11" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="U11" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="V11" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="W11" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X11" s="34" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
         <v>10</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>10</v>
+      <c r="B12" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>13</v>
       </c>
       <c r="I12" s="22">
         <v>10</v>
       </c>
-      <c r="L12" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="O12" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="P12" s="25" t="s">
-        <v>12</v>
+      <c r="J12" s="27"/>
+      <c r="K12" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="O12" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="35" t="s">
+        <v>58</v>
       </c>
       <c r="Q12" s="22">
         <v>10</v>
       </c>
-      <c r="R12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="S12" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="T12" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="U12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="V12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W12" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="X12" s="25" t="s">
-        <v>14</v>
+      <c r="R12" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="S12" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="T12" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="U12" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="V12" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="W12" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="X12" s="30" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="22">
         <v>11</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>11</v>
+      <c r="B13" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>57</v>
       </c>
       <c r="I13" s="22">
         <v>11</v>
       </c>
-      <c r="J13" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="L13" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="O13" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="P13" s="25" t="s">
-        <v>13</v>
-      </c>
+      <c r="J13" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="27"/>
       <c r="Q13" s="22">
         <v>11</v>
       </c>
-      <c r="R13" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="S13" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T13" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="U13" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="V13" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="W13" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="X13" s="25" t="s">
-        <v>15</v>
+      <c r="R13" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="S13" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="U13" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="V13" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="W13" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="X13" s="33" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
-        <v>12</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="27">
-        <v>12</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="N14" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="O14" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="P14" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q14" s="27">
-        <v>12</v>
-      </c>
-      <c r="R14" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="S14" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="T14" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="U14" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="V14" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="W14" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="X14" s="25" t="s">
-        <v>14</v>
-      </c>
+      <c r="A14" s="25">
+        <v>12</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="25">
+        <v>12</v>
+      </c>
+      <c r="J14" s="27"/>
+      <c r="K14" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="O14" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="P14" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q14" s="25">
+        <v>12</v>
+      </c>
+      <c r="R14" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="S14" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="T14" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="U14" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="V14" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="W14" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X14" s="34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="41">
+        <v>13</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="41">
+        <v>13</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="28"/>
+      <c r="M15" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="O15" s="28"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="41">
+        <v>13</v>
+      </c>
+      <c r="R15" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="S15" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="T15" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="U15" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="V15" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="W15" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="X15" s="33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="41">
+        <v>14</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="41">
+        <v>14</v>
+      </c>
+      <c r="J16" s="27"/>
+      <c r="K16" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" s="28"/>
+      <c r="M16" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="O16" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="P16" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="41">
+        <v>14</v>
+      </c>
+      <c r="R16" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="S16" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="T16" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="U16" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="V16" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="W16" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="X16" s="34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="26"/>
+      <c r="W26" s="26"/>
+      <c r="X26" s="26"/>
+      <c r="Y26" s="26"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A27" s="26"/>
+      <c r="R27" s="28"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A28" s="26"/>
+      <c r="R28" s="28"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A29" s="26"/>
+      <c r="R29" s="28"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A30" s="26"/>
+      <c r="R30" s="28"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A31" s="26"/>
+      <c r="R31" s="28"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A32" s="26"/>
+      <c r="R32" s="28"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="26"/>
+      <c r="R33" s="28"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="26"/>
+      <c r="R34" s="28"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="26"/>
+      <c r="R35" s="28"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="26"/>
+      <c r="R36" s="28"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="26"/>
+      <c r="R37" s="28"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="26"/>
+      <c r="R38" s="28"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="26"/>
+      <c r="R39" s="28"/>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="26"/>
+      <c r="R40" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1816,33 +2212,33 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="48"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="37"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="51"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
@@ -2464,35 +2860,35 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="48"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="37"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="51"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -3541,35 +3937,35 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="48"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="37"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="51"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -4548,35 +4944,35 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="34"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="48"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="37"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="51"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -5556,15 +5952,15 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="37"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
@@ -5778,15 +6174,15 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -6000,15 +6396,15 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -6222,15 +6618,15 @@
   <sheetData>
     <row r="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B1" s="2"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="51"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="4"/>
@@ -6444,15 +6840,15 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
